--- a/HM.BST.xlsx
+++ b/HM.BST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37697899-236B-4999-B371-486648B82E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FE6775-EC63-4428-BE80-C5B16A3208E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{A344954E-3009-47EB-94FE-5B6CEBCD1700}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{A344954E-3009-47EB-94FE-5B6CEBCD1700}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>166.25</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -911,10 +911,10 @@
         <v>11</v>
       </c>
       <c r="I3" s="3">
-        <v>1597.6010000000001</v>
+        <v>1596.373</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -926,7 +926,7 @@
       </c>
       <c r="I4" s="6">
         <f>I3*I2</f>
-        <v>265601.16625000001</v>
+        <v>257415.14625000002</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -938,10 +938,10 @@
         <v>13</v>
       </c>
       <c r="I5" s="6">
-        <v>18697</v>
+        <v>26507</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -953,7 +953,7 @@
         <v>20675</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -965,7 +965,7 @@
       </c>
       <c r="I7" s="6">
         <f>I4+I6-I5</f>
-        <v>267579.16625000001</v>
+        <v>251583.14624999999</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1147,7 +1147,9 @@
       <c r="P3" s="16">
         <v>3599</v>
       </c>
-      <c r="Q3" s="16"/>
+      <c r="Q3" s="16">
+        <v>3579</v>
+      </c>
       <c r="R3" s="16"/>
       <c r="S3" s="16"/>
       <c r="T3" s="16">
@@ -1285,7 +1287,9 @@
       <c r="P4" s="16">
         <v>252</v>
       </c>
-      <c r="Q4" s="16"/>
+      <c r="Q4" s="16">
+        <v>257</v>
+      </c>
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
       <c r="T4" s="16">
@@ -1423,7 +1427,9 @@
       <c r="P5" s="16">
         <v>0</v>
       </c>
-      <c r="Q5" s="16"/>
+      <c r="Q5" s="16">
+        <v>0</v>
+      </c>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
       <c r="T5" s="16">
@@ -1561,7 +1567,9 @@
       <c r="P6" s="16">
         <v>44</v>
       </c>
-      <c r="Q6" s="16"/>
+      <c r="Q6" s="16">
+        <v>44</v>
+      </c>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
       <c r="T6" s="16">
@@ -1699,7 +1707,9 @@
       <c r="P7" s="16">
         <v>65</v>
       </c>
-      <c r="Q7" s="16"/>
+      <c r="Q7" s="16">
+        <v>65</v>
+      </c>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16">
@@ -1837,7 +1847,9 @@
       <c r="P8" s="16">
         <v>55</v>
       </c>
-      <c r="Q8" s="16"/>
+      <c r="Q8" s="16">
+        <v>59</v>
+      </c>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
       <c r="T8" s="16">
@@ -1975,7 +1987,9 @@
       <c r="P9" s="16">
         <v>0</v>
       </c>
-      <c r="Q9" s="16"/>
+      <c r="Q9" s="16">
+        <v>0</v>
+      </c>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
       <c r="T9" s="16">
@@ -2113,7 +2127,9 @@
       <c r="P10" s="16">
         <v>23</v>
       </c>
-      <c r="Q10" s="16"/>
+      <c r="Q10" s="16">
+        <v>19</v>
+      </c>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
       <c r="T10" s="16">
@@ -2251,7 +2267,9 @@
       <c r="P11" s="16">
         <v>0</v>
       </c>
-      <c r="Q11" s="16"/>
+      <c r="Q11" s="16">
+        <v>0</v>
+      </c>
       <c r="R11" s="16"/>
       <c r="S11" s="16"/>
       <c r="T11" s="16">
@@ -2389,7 +2407,9 @@
       <c r="P12" s="16">
         <v>354</v>
       </c>
-      <c r="Q12" s="16"/>
+      <c r="Q12" s="16">
+        <v>352</v>
+      </c>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
       <c r="T12" s="16">
@@ -2527,7 +2547,9 @@
       <c r="P13" s="16">
         <v>985</v>
       </c>
-      <c r="Q13" s="16"/>
+      <c r="Q13" s="16">
+        <v>985</v>
+      </c>
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
       <c r="T13" s="16">
@@ -2665,7 +2687,9 @@
       <c r="P14" s="16">
         <v>473</v>
       </c>
-      <c r="Q14" s="16"/>
+      <c r="Q14" s="16">
+        <v>473</v>
+      </c>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
       <c r="T14" s="16">
@@ -2803,7 +2827,9 @@
       <c r="P15" s="16">
         <v>564</v>
       </c>
-      <c r="Q15" s="16"/>
+      <c r="Q15" s="16">
+        <v>566</v>
+      </c>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
       <c r="T15" s="16">
@@ -2941,7 +2967,9 @@
       <c r="P16" s="16">
         <v>761</v>
       </c>
-      <c r="Q16" s="16"/>
+      <c r="Q16" s="16">
+        <v>761</v>
+      </c>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
       <c r="T16" s="16">
@@ -3079,7 +3107,9 @@
       <c r="P17" s="16">
         <v>901</v>
       </c>
-      <c r="Q17" s="16"/>
+      <c r="Q17" s="16">
+        <v>886</v>
+      </c>
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
       <c r="T17" s="16">
@@ -3217,7 +3247,9 @@
       <c r="P18" s="17">
         <v>4038</v>
       </c>
-      <c r="Q18" s="17"/>
+      <c r="Q18" s="17">
+        <v>4023</v>
+      </c>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
       <c r="T18" s="17">
@@ -3460,7 +3492,9 @@
       <c r="P20" s="16">
         <v>5176</v>
       </c>
-      <c r="Q20" s="16"/>
+      <c r="Q20" s="16">
+        <v>5595</v>
+      </c>
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
@@ -3596,7 +3630,9 @@
       <c r="P21" s="16">
         <v>18975</v>
       </c>
-      <c r="Q21" s="16"/>
+      <c r="Q21" s="16">
+        <v>19414</v>
+      </c>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
@@ -3732,7 +3768,9 @@
       <c r="P22" s="16">
         <v>4989</v>
       </c>
-      <c r="Q22" s="16"/>
+      <c r="Q22" s="16">
+        <v>5431</v>
+      </c>
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
@@ -3868,7 +3906,9 @@
       <c r="P23" s="16">
         <v>7484</v>
       </c>
-      <c r="Q23" s="16"/>
+      <c r="Q23" s="16">
+        <v>7764</v>
+      </c>
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
@@ -4004,7 +4044,9 @@
       <c r="P24" s="16">
         <v>11530</v>
       </c>
-      <c r="Q24" s="16"/>
+      <c r="Q24" s="16">
+        <v>12457</v>
+      </c>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
@@ -4140,7 +4182,9 @@
       <c r="P25" s="16">
         <v>6674</v>
       </c>
-      <c r="Q25" s="16"/>
+      <c r="Q25" s="16">
+        <v>6528</v>
+      </c>
       <c r="R25" s="16"/>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
@@ -4276,7 +4320,9 @@
       <c r="P26" s="17">
         <v>54828</v>
       </c>
-      <c r="Q26" s="17"/>
+      <c r="Q26" s="17">
+        <v>57189</v>
+      </c>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
       <c r="T26" s="17">
@@ -4416,7 +4462,9 @@
       <c r="P27" s="16">
         <v>23783</v>
       </c>
-      <c r="Q27" s="16"/>
+      <c r="Q27" s="16">
+        <v>26322</v>
+      </c>
       <c r="R27" s="16"/>
       <c r="S27" s="16"/>
       <c r="T27" s="16">
@@ -4533,7 +4581,7 @@
         <v>27655</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28:P28" si="4">H26-H27</f>
+        <f t="shared" ref="H28:Q28" si="4">H26-H27</f>
         <v>33569</v>
       </c>
       <c r="I28" s="16">
@@ -4568,7 +4616,10 @@
         <f t="shared" si="4"/>
         <v>31045</v>
       </c>
-      <c r="Q28" s="16"/>
+      <c r="Q28" s="16">
+        <f t="shared" si="4"/>
+        <v>30867</v>
+      </c>
       <c r="R28" s="16"/>
       <c r="S28" s="16"/>
       <c r="T28" s="16">
@@ -4713,7 +4764,9 @@
       <c r="P29" s="16">
         <v>22333</v>
       </c>
-      <c r="Q29" s="16"/>
+      <c r="Q29" s="16">
+        <v>22302</v>
+      </c>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
       <c r="T29" s="16">
@@ -4853,7 +4906,9 @@
       <c r="P30" s="16">
         <v>2800</v>
       </c>
-      <c r="Q30" s="16"/>
+      <c r="Q30" s="16">
+        <v>2530</v>
+      </c>
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
       <c r="T30" s="16">
@@ -4993,7 +5048,9 @@
       <c r="P31" s="16">
         <v>1</v>
       </c>
-      <c r="Q31" s="16"/>
+      <c r="Q31" s="16">
+        <v>2</v>
+      </c>
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
       <c r="T31" s="16">
@@ -5110,7 +5167,7 @@
         <v>2077</v>
       </c>
       <c r="H32" s="16">
-        <f t="shared" ref="H32:P32" si="7">H28-SUM(H29:H30)+H31</f>
+        <f t="shared" ref="H32:Q32" si="7">H28-SUM(H29:H30)+H31</f>
         <v>7098</v>
       </c>
       <c r="I32" s="16">
@@ -5145,7 +5202,10 @@
         <f t="shared" si="7"/>
         <v>5913</v>
       </c>
-      <c r="Q32" s="16"/>
+      <c r="Q32" s="16">
+        <f t="shared" si="7"/>
+        <v>6037</v>
+      </c>
       <c r="R32" s="16"/>
       <c r="S32" s="16"/>
       <c r="T32" s="16">
@@ -5291,7 +5351,9 @@
       <c r="P33" s="16">
         <v>-629</v>
       </c>
-      <c r="Q33" s="16"/>
+      <c r="Q33" s="16">
+        <v>-574</v>
+      </c>
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
       <c r="T33" s="16">
@@ -5413,7 +5475,7 @@
         <v>1606</v>
       </c>
       <c r="H34" s="16">
-        <f t="shared" ref="H34:P34" si="10">H32+H33</f>
+        <f t="shared" ref="H34:Q34" si="10">H32+H33</f>
         <v>6668</v>
       </c>
       <c r="I34" s="16">
@@ -5448,7 +5510,10 @@
         <f t="shared" si="10"/>
         <v>5284</v>
       </c>
-      <c r="Q34" s="16"/>
+      <c r="Q34" s="16">
+        <f t="shared" si="10"/>
+        <v>5463</v>
+      </c>
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
       <c r="T34" s="16">
@@ -5593,7 +5658,9 @@
       <c r="P35" s="16">
         <v>1321</v>
       </c>
-      <c r="Q35" s="16"/>
+      <c r="Q35" s="16">
+        <v>1365</v>
+      </c>
       <c r="R35" s="16"/>
       <c r="S35" s="16"/>
       <c r="T35" s="16">
@@ -5710,7 +5777,7 @@
         <v>1201</v>
       </c>
       <c r="H36" s="16">
-        <f t="shared" ref="H36:P36" si="14">H34-H35</f>
+        <f t="shared" ref="H36:Q36" si="14">H34-H35</f>
         <v>4995</v>
       </c>
       <c r="I36" s="16">
@@ -5745,7 +5812,10 @@
         <f t="shared" si="14"/>
         <v>3963</v>
       </c>
-      <c r="Q36" s="16"/>
+      <c r="Q36" s="16">
+        <f t="shared" si="14"/>
+        <v>4098</v>
+      </c>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
       <c r="T36" s="16">
@@ -5890,7 +5960,9 @@
       <c r="P37" s="16">
         <v>23</v>
       </c>
-      <c r="Q37" s="16"/>
+      <c r="Q37" s="16">
+        <v>25</v>
+      </c>
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
       <c r="T37" s="16">
@@ -6007,7 +6079,7 @@
         <v>1209</v>
       </c>
       <c r="H38" s="16">
-        <f t="shared" ref="H38:P38" si="16">H36+H37</f>
+        <f t="shared" ref="H38:Q38" si="16">H36+H37</f>
         <v>5008</v>
       </c>
       <c r="I38" s="16">
@@ -6042,7 +6114,10 @@
         <f t="shared" si="16"/>
         <v>3986</v>
       </c>
-      <c r="Q38" s="16"/>
+      <c r="Q38" s="16">
+        <f t="shared" si="16"/>
+        <v>4123</v>
+      </c>
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
       <c r="T38" s="16">
@@ -6261,7 +6336,7 @@
         <v>0.74745207867721386</v>
       </c>
       <c r="H40" s="18">
-        <f t="shared" ref="H40:P40" si="18">H38/H41</f>
+        <f t="shared" ref="H40:Q40" si="18">H38/H41</f>
         <v>3.1095122014824823</v>
       </c>
       <c r="I40" s="18">
@@ -6296,7 +6371,10 @@
         <f t="shared" si="18"/>
         <v>2.4949909270212021</v>
       </c>
-      <c r="Q40" s="18"/>
+      <c r="Q40" s="18">
+        <f t="shared" si="18"/>
+        <v>2.582729725446371</v>
+      </c>
       <c r="R40" s="18"/>
       <c r="S40" s="18"/>
       <c r="T40" s="18">
@@ -6441,7 +6519,9 @@
       <c r="P41" s="3">
         <v>1597.6010000000001</v>
       </c>
-      <c r="Q41" s="3"/>
+      <c r="Q41" s="3">
+        <v>1596.373</v>
+      </c>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3">
@@ -6655,35 +6735,38 @@
         <v>-7.2944932162809506E-3</v>
       </c>
       <c r="K43" s="19">
-        <f>+K26/G26-1</f>
+        <f t="shared" ref="K43:Q43" si="21">+K26/G26-1</f>
         <v>3.1004863142596317E-2</v>
       </c>
       <c r="L43" s="19">
-        <f>+L26/H26-1</f>
+        <f t="shared" si="21"/>
         <v>-4.8502642395772178E-2</v>
       </c>
       <c r="M43" s="19">
-        <f>+M26/I26-1</f>
+        <f t="shared" si="21"/>
         <v>-3.3790310281133995E-2</v>
       </c>
       <c r="N43" s="19">
-        <f>+N26/J26-1</f>
+        <f t="shared" si="21"/>
         <v>-4.7786728409949686E-2</v>
       </c>
       <c r="O43" s="19">
-        <f>+O26/K26-1</f>
+        <f t="shared" si="21"/>
         <v>-0.10348255109970539</v>
       </c>
       <c r="P43" s="19">
-        <f>+P26/L26-1</f>
+        <f t="shared" si="21"/>
         <v>-3.3254575589801494E-2</v>
       </c>
-      <c r="Q43" s="19"/>
+      <c r="Q43" s="19">
+        <f t="shared" si="21"/>
+        <v>3.0166441587595738E-3</v>
+      </c>
       <c r="R43" s="19"/>
       <c r="S43" s="20"/>
       <c r="T43" s="19"/>
       <c r="U43" s="19">
-        <f t="shared" ref="U43" si="21">U26/T26-1</f>
+        <f t="shared" ref="U43" si="22">U26/T26-1</f>
         <v>0.12356822990747207</v>
       </c>
       <c r="V43" s="19">
@@ -6777,19 +6860,19 @@
         <v>29</v>
       </c>
       <c r="C44" s="21">
-        <f t="shared" ref="C44:F44" si="22">C28/C26</f>
+        <f t="shared" ref="C44:F44" si="23">C28/C26</f>
         <v>0.47175244204694561</v>
       </c>
       <c r="D44" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.52655512357678425</v>
       </c>
       <c r="E44" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.50930259290277025</v>
       </c>
       <c r="F44" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.53722266560255383</v>
       </c>
       <c r="G44" s="21">
@@ -6797,50 +6880,53 @@
         <v>0.51528815517337756</v>
       </c>
       <c r="H44" s="21">
-        <f t="shared" ref="H44:K44" si="23">H28/H26</f>
+        <f t="shared" ref="H44:K44" si="24">H28/H26</f>
         <v>0.56319100746581663</v>
       </c>
       <c r="I44" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.51063361068275404</v>
       </c>
       <c r="J44" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.54575273744633646</v>
       </c>
       <c r="K44" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.49100898198181919</v>
       </c>
       <c r="L44" s="21">
-        <f t="shared" ref="L44:M44" si="24">L28/L26</f>
+        <f t="shared" ref="L44:M44" si="25">L28/L26</f>
         <v>0.55409599040801216</v>
       </c>
       <c r="M44" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.5286668888226318</v>
       </c>
       <c r="N44" s="21">
-        <f t="shared" ref="N44:O44" si="25">N28/N26</f>
+        <f t="shared" ref="N44:O44" si="26">N28/N26</f>
         <v>0.5586531804596343</v>
       </c>
       <c r="O44" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.50674299997984151</v>
       </c>
       <c r="P44" s="21">
-        <f t="shared" ref="P44" si="26">P28/P26</f>
+        <f t="shared" ref="P44:Q44" si="27">P28/P26</f>
         <v>0.5662252863500401</v>
       </c>
-      <c r="Q44" s="21"/>
+      <c r="Q44" s="21">
+        <f t="shared" si="27"/>
+        <v>0.53973666264491427</v>
+      </c>
       <c r="R44" s="21"/>
       <c r="S44" s="3"/>
       <c r="T44" s="21">
-        <f t="shared" ref="T44:U44" si="27">T28/T26</f>
+        <f t="shared" ref="T44:U44" si="28">T28/T26</f>
         <v>0.52775585901179589</v>
       </c>
       <c r="U44" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.50712806359118423</v>
       </c>
       <c r="V44" s="21">
@@ -6934,19 +7020,19 @@
         <v>30</v>
       </c>
       <c r="C45" s="21">
-        <f t="shared" ref="C45:F45" si="28">C32/C26</f>
+        <f t="shared" ref="C45:F45" si="29">C32/C26</f>
         <v>1.3212567429654468E-2</v>
       </c>
       <c r="D45" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8.2286170508192175E-2</v>
       </c>
       <c r="E45" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.781992544788742E-2</v>
       </c>
       <c r="F45" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>6.9146049481245017E-2</v>
       </c>
       <c r="G45" s="21">
@@ -6954,50 +7040,53 @@
         <v>3.8700180737483464E-2</v>
       </c>
       <c r="H45" s="21">
-        <f t="shared" ref="H45:K45" si="29">H32/H26</f>
+        <f t="shared" ref="H45:K45" si="30">H32/H26</f>
         <v>0.11908396946564885</v>
       </c>
       <c r="I45" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>5.9429597871583265E-2</v>
       </c>
       <c r="J45" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.43492032865435E-2</v>
       </c>
       <c r="K45" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.1741094825872446E-2</v>
       </c>
       <c r="L45" s="21">
-        <f t="shared" ref="L45:M45" si="30">L32/L26</f>
+        <f t="shared" ref="L45:M45" si="31">L32/L26</f>
         <v>0.10427760341361922</v>
       </c>
       <c r="M45" s="21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.6184822070610526E-2</v>
       </c>
       <c r="N45" s="21">
-        <f t="shared" ref="N45:O45" si="31">N32/N26</f>
+        <f t="shared" ref="N45:O45" si="32">N32/N26</f>
         <v>0.10746188007632428</v>
       </c>
       <c r="O45" s="21">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.0479569415606669E-2</v>
       </c>
       <c r="P45" s="21">
-        <f t="shared" ref="P45" si="32">P32/P26</f>
+        <f t="shared" ref="P45:Q45" si="33">P32/P26</f>
         <v>0.10784635587655943</v>
       </c>
-      <c r="Q45" s="21"/>
+      <c r="Q45" s="21">
+        <f t="shared" si="33"/>
+        <v>0.10556225847628041</v>
+      </c>
       <c r="R45" s="21"/>
       <c r="S45" s="3"/>
       <c r="T45" s="21">
-        <f t="shared" ref="T45:U45" si="33">T32/T26</f>
+        <f t="shared" ref="T45:U45" si="34">T32/T26</f>
         <v>7.6671005744671228E-2</v>
       </c>
       <c r="U45" s="21">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3.206845803903325E-2</v>
       </c>
       <c r="V45" s="21">
@@ -7091,19 +7180,19 @@
         <v>31</v>
       </c>
       <c r="C46" s="21">
-        <f t="shared" ref="C46:F46" si="34">C38/C26</f>
+        <f t="shared" ref="C46:F46" si="35">C38/C26</f>
         <v>9.8593089371628514E-3</v>
       </c>
       <c r="D46" s="21">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.7206331574562619E-2</v>
       </c>
       <c r="E46" s="21">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.4649654334367866E-2</v>
       </c>
       <c r="F46" s="21">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.5331205107741419E-2</v>
       </c>
       <c r="G46" s="21">
@@ -7111,50 +7200,53 @@
         <v>2.2526970877042612E-2</v>
       </c>
       <c r="H46" s="21">
-        <f t="shared" ref="H46:K46" si="35">H38/H26</f>
+        <f t="shared" ref="H46:K46" si="36">H38/H26</f>
         <v>8.401979699689624E-2</v>
       </c>
       <c r="I46" s="21">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.9297758045110237E-2</v>
       </c>
       <c r="J46" s="21">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>4.9603653144244531E-2</v>
       </c>
       <c r="K46" s="21">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.066271483563154E-2</v>
       </c>
       <c r="L46" s="21">
-        <f t="shared" ref="L46:M46" si="36">L38/L26</f>
+        <f t="shared" ref="L46:M46" si="37">L38/L26</f>
         <v>7.0123778961103084E-2</v>
       </c>
       <c r="M46" s="21">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.6632232492063769E-2</v>
       </c>
       <c r="N46" s="21">
-        <f t="shared" ref="N46:O46" si="37">N38/N26</f>
+        <f t="shared" ref="N46:O46" si="38">N38/N26</f>
         <v>7.3656304351496935E-2</v>
       </c>
       <c r="O46" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1.4594714455621183E-2</v>
       </c>
       <c r="P46" s="21">
-        <f t="shared" ref="P46" si="38">P38/P26</f>
+        <f t="shared" ref="P46:Q46" si="39">P38/P26</f>
         <v>7.2700080250966664E-2</v>
       </c>
-      <c r="Q46" s="21"/>
+      <c r="Q46" s="21">
+        <f t="shared" si="39"/>
+        <v>7.2094283865778389E-2</v>
+      </c>
       <c r="R46" s="21"/>
       <c r="S46" s="3"/>
       <c r="T46" s="21">
-        <f t="shared" ref="T46:U46" si="39">T38/T26</f>
+        <f t="shared" ref="T46:U46" si="40">T38/T26</f>
         <v>5.5335809455839408E-2</v>
       </c>
       <c r="U46" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.5951474594391488E-2</v>
       </c>
       <c r="V46" s="21">
@@ -7248,19 +7340,19 @@
         <v>32</v>
       </c>
       <c r="C47" s="21">
-        <f t="shared" ref="C47:F47" si="40">C35/C34</f>
+        <f t="shared" ref="C47:F47" si="41">C35/C34</f>
         <v>-0.36363636363636365</v>
       </c>
       <c r="D47" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.23976878612716762</v>
       </c>
       <c r="E47" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.24102446832837868</v>
       </c>
       <c r="F47" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.59754851889683347</v>
       </c>
       <c r="G47" s="21">
@@ -7268,50 +7360,53 @@
         <v>0.25217932752179328</v>
       </c>
       <c r="H47" s="21">
-        <f t="shared" ref="H47:K47" si="41">H35/H34</f>
+        <f t="shared" ref="H47:K47" si="42">H35/H34</f>
         <v>0.25089982003599282</v>
       </c>
       <c r="I47" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.25218800648298217</v>
       </c>
       <c r="J47" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.24559255631733595</v>
       </c>
       <c r="K47" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.24015748031496062</v>
       </c>
       <c r="L47" s="21">
-        <f t="shared" ref="L47:M47" si="42">L35/L34</f>
+        <f t="shared" ref="L47:M47" si="43">L35/L34</f>
         <v>0.25118125118125118</v>
       </c>
       <c r="M47" s="21">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.25682554372975475</v>
       </c>
       <c r="N47" s="21">
-        <f t="shared" ref="N47:O47" si="43">N35/N34</f>
+        <f t="shared" ref="N47:O47" si="44">N35/N34</f>
         <v>0.25656426977861679</v>
       </c>
       <c r="O47" s="21">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.25026624068157616</v>
       </c>
       <c r="P47" s="21">
-        <f t="shared" ref="P47" si="44">P35/P34</f>
+        <f t="shared" ref="P47:Q47" si="45">P35/P34</f>
         <v>0.25</v>
       </c>
-      <c r="Q47" s="21"/>
+      <c r="Q47" s="21">
+        <f t="shared" si="45"/>
+        <v>0.2498627127951675</v>
+      </c>
       <c r="R47" s="21"/>
       <c r="S47" s="3"/>
       <c r="T47" s="21">
-        <f t="shared" ref="T47:U47" si="45">T35/T34</f>
+        <f t="shared" ref="T47:U47" si="46">T35/T34</f>
         <v>0.23006993006993007</v>
       </c>
       <c r="U47" s="21">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.42631917631917632</v>
       </c>
       <c r="V47" s="21">
